--- a/Gmail_Compose_TestCases.xlsx
+++ b/Gmail_Compose_TestCases.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8116B0-2E9B-4CB9-B6BA-17F1819BB4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD7A117-34C6-41DF-A281-6AFB108F2C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Traditional_TestCases" sheetId="1" r:id="rId1"/>
     <sheet name="BDD_TestCases" sheetId="2" r:id="rId2"/>
+    <sheet name="Coverage" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="193">
   <si>
     <t>TC_ID</t>
   </si>
@@ -44,6 +45,24 @@
     <t>TC_01</t>
   </si>
   <si>
+    <t>Verify compose window opens</t>
+  </si>
+  <si>
+    <t>Click Compose button</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Compose popup should open</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>TC_02</t>
+  </si>
+  <si>
     <t>Verify user can compose email successfully</t>
   </si>
   <si>
@@ -56,24 +75,6 @@
     <t>Email sent successfully</t>
   </si>
   <si>
-    <t>Positive</t>
-  </si>
-  <si>
-    <t>TC_02</t>
-  </si>
-  <si>
-    <t>Verify compose window opens</t>
-  </si>
-  <si>
-    <t>Click Compose button</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Compose popup should open</t>
-  </si>
-  <si>
     <t>TC_03</t>
   </si>
   <si>
@@ -224,6 +225,219 @@
     <t>Content should save properly</t>
   </si>
   <si>
+    <t>TC_13</t>
+  </si>
+  <si>
+    <t>Verify email sending with CC recipients</t>
+  </si>
+  <si>
+    <t>Add CC recipient and send email</t>
+  </si>
+  <si>
+    <t>CC Email</t>
+  </si>
+  <si>
+    <t>Email should send successfully</t>
+  </si>
+  <si>
+    <t>TC_14</t>
+  </si>
+  <si>
+    <t>Verify email sending with BCC recipients</t>
+  </si>
+  <si>
+    <t>Add BCC recipient and send email</t>
+  </si>
+  <si>
+    <t>BCC Email</t>
+  </si>
+  <si>
+    <t>TC_15</t>
+  </si>
+  <si>
+    <t>Verify maximum character limit in subject field</t>
+  </si>
+  <si>
+    <t>Enter maximum allowed characters in subject</t>
+  </si>
+  <si>
+    <t>Long Subject</t>
+  </si>
+  <si>
+    <t>Subject should handle limit properly</t>
+  </si>
+  <si>
+    <t>Boundary</t>
+  </si>
+  <si>
+    <t>TC_16</t>
+  </si>
+  <si>
+    <t>Verify very long email body content</t>
+  </si>
+  <si>
+    <t>Enter large body content</t>
+  </si>
+  <si>
+    <t>Long Body</t>
+  </si>
+  <si>
+    <t>Body should support long text</t>
+  </si>
+  <si>
+    <t>TC_17</t>
+  </si>
+  <si>
+    <t>Verify sending email with empty subject</t>
+  </si>
+  <si>
+    <t>Leave subject empty and click Send</t>
+  </si>
+  <si>
+    <t>Empty Subject</t>
+  </si>
+  <si>
+    <t>Warning popup should appear</t>
+  </si>
+  <si>
+    <t>TC_18</t>
+  </si>
+  <si>
+    <t>Verify browser refresh during draft creation</t>
+  </si>
+  <si>
+    <t>Refresh browser while composing</t>
+  </si>
+  <si>
+    <t>Draft Content</t>
+  </si>
+  <si>
+    <t>Draft should persist</t>
+  </si>
+  <si>
+    <t>TC_19</t>
+  </si>
+  <si>
+    <t>Verify session timeout while composing</t>
+  </si>
+  <si>
+    <t>Expire session and try to send email</t>
+  </si>
+  <si>
+    <t>Session Timeout</t>
+  </si>
+  <si>
+    <t>Login/session warning should appear</t>
+  </si>
+  <si>
+    <t>TC_20</t>
+  </si>
+  <si>
+    <t>Verify keyboard shortcut (Ctrl + Enter) for send</t>
+  </si>
+  <si>
+    <t>Press Ctrl + Enter after entering details</t>
+  </si>
+  <si>
+    <t>TC_21</t>
+  </si>
+  <si>
+    <t>Verify unsupported file type attachment</t>
+  </si>
+  <si>
+    <t>Upload unsupported file</t>
+  </si>
+  <si>
+    <t>Unsupported File</t>
+  </si>
+  <si>
+    <t>Validation/error should appear</t>
+  </si>
+  <si>
+    <t>TC_22</t>
+  </si>
+  <si>
+    <t>Verify drag-and-drop attachment upload</t>
+  </si>
+  <si>
+    <t>Drag file into compose area</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>TC_23</t>
+  </si>
+  <si>
+    <t>Verify compose window minimization</t>
+  </si>
+  <si>
+    <t>Minimize compose popup</t>
+  </si>
+  <si>
+    <t>Draft should remain intact</t>
+  </si>
+  <si>
+    <t>TC_24</t>
+  </si>
+  <si>
+    <t>Verify spell check behavior in email body</t>
+  </si>
+  <si>
+    <t>Type misspelled words</t>
+  </si>
+  <si>
+    <t>Spelling Errors</t>
+  </si>
+  <si>
+    <t>Misspelled words should highlight</t>
+  </si>
+  <si>
+    <t>TC_25</t>
+  </si>
+  <si>
+    <t>Verify email sending during slow network</t>
+  </si>
+  <si>
+    <t>Send email on slow internet</t>
+  </si>
+  <si>
+    <t>Slow Network</t>
+  </si>
+  <si>
+    <t>Proper loader/retry handling should happen</t>
+  </si>
+  <si>
+    <t>TC_26</t>
+  </si>
+  <si>
+    <t>Verify duplicate recipient emails</t>
+  </si>
+  <si>
+    <t>Enter same recipient multiple times</t>
+  </si>
+  <si>
+    <t>Duplicate Emails</t>
+  </si>
+  <si>
+    <t>Email should send properly</t>
+  </si>
+  <si>
+    <t>TC_27</t>
+  </si>
+  <si>
+    <t>Verify Unicode characters/emojis in body</t>
+  </si>
+  <si>
+    <t>Enter emojis and Unicode chars</t>
+  </si>
+  <si>
+    <t>😊 తెలుగు</t>
+  </si>
+  <si>
+    <t>Content should display correctly</t>
+  </si>
+  <si>
     <t>Feature</t>
   </si>
   <si>
@@ -317,7 +531,76 @@
     <t>User clicks Send</t>
   </si>
   <si>
-    <t>Email should send successfully</t>
+    <t>Send email using keyboard shortcut</t>
+  </si>
+  <si>
+    <t>User enters valid details</t>
+  </si>
+  <si>
+    <t>User presses Ctrl + Enter</t>
+  </si>
+  <si>
+    <t>Send email without subject</t>
+  </si>
+  <si>
+    <t>User enters recipient and body only</t>
+  </si>
+  <si>
+    <t>Upload attachment via drag-drop</t>
+  </si>
+  <si>
+    <t>User drags file into compose area</t>
+  </si>
+  <si>
+    <t>File should upload successfully</t>
+  </si>
+  <si>
+    <t>Compose during session timeout</t>
+  </si>
+  <si>
+    <t>User session expires</t>
+  </si>
+  <si>
+    <t>User attempts to send email</t>
+  </si>
+  <si>
+    <t>Login/session warning should display</t>
+  </si>
+  <si>
+    <t>Minimize compose window</t>
+  </si>
+  <si>
+    <t>User creates draft</t>
+  </si>
+  <si>
+    <t>User minimizes compose popup</t>
+  </si>
+  <si>
+    <t>Draft should remain saved</t>
+  </si>
+  <si>
+    <t>Testing Coverage</t>
+  </si>
+  <si>
+    <t>Functional Testing</t>
+  </si>
+  <si>
+    <t>UI Testing</t>
+  </si>
+  <si>
+    <t>Validation Testing</t>
+  </si>
+  <si>
+    <t>Boundary Testing</t>
+  </si>
+  <si>
+    <t>Usability Testing</t>
+  </si>
+  <si>
+    <t>Error Handling Testing</t>
+  </si>
+  <si>
+    <t>Positive &amp; Negative Scenarios</t>
   </si>
 </sst>
 </file>
@@ -335,6 +618,7 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -347,12 +631,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -375,191 +659,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -863,39 +973,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="47" customWidth="1"/>
+    <col min="2" max="2" width="53" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="5" max="5" width="47" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -910,227 +1020,527 @@
       <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1141,167 +1551,305 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="2" max="2" width="39" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="60" customWidth="1"/>
     <col min="5" max="5" width="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1" s="10" t="s">
+      <c r="A1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7" s="1" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>98</v>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
